--- a/multiSchoolOutput/01_School_of_Divinity/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/01_School_of_Divinity/solution_weeks_9_10.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0228_01_1.01</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1354,7 +1354,7 @@
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0003_00_G.04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0228_06_6.05</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0335_00_G.17</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0228_11_11.06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2313,12 +2313,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0228_01_1.01</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0113_01M_01M.19</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0008_02_2.418</t>
+          <t>0228_11_11.06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0201_07_7.14</t>
+          <t>0228_07_7.01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3916,7 +3916,7 @@
         <v>6</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4021,12 +4021,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0228_06_6.05</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0113_02_2.26</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0008_-1_B.152</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0008_02_2.418</t>
+          <t>0201_02_2.06</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0008_-1_B.152</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0113_00_G.205</t>
+          <t>0113_01M_01M.19</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0113_01M_01M.20</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0201_07_7.14</t>
+          <t>0228_07_7.01</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0113_01M_01M.20</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0450_03_3.62</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0003_00_G.04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0113_00_G.205</t>
+          <t>0008_-1_B.152</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0254_01_1.10</t>
+          <t>0008_-1_B.152</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0450_03_3.62</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>5</v>
       </c>
       <c r="F113" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">

--- a/multiSchoolOutput/01_School_of_Divinity/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/01_School_of_Divinity/solution_weeks_9_10.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0113_00_G.07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -567,7 +567,7 @@
         <v>120</v>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -685,7 +685,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -727,12 +727,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -744,7 +744,7 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -788,12 +788,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -805,7 +805,7 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0219_00_G.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -927,7 +927,7 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0005_-1_B.01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -988,7 +988,7 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1171,7 +1171,7 @@
         <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0254_01_1.10</t>
+          <t>0113_01M_01M.19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_01M_01M.19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1354,7 +1354,7 @@
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0228_03_3.01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1415,7 +1415,7 @@
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1476,7 +1476,7 @@
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1537,7 +1537,7 @@
         <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0228_01_1.01</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0228_01_1.01</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0228_06_6.05</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1903,7 +1903,7 @@
         <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0228_11_11.06</t>
+          <t>0214_00_G.22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2025,7 +2025,7 @@
         <v>216</v>
       </c>
       <c r="F27" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2086,7 +2086,7 @@
         <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0228_06_6.11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2269,7 +2269,7 @@
         <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2313,12 +2313,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0228_06_6.05</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0227_02_2.54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2574,7 +2574,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2618,12 +2618,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2635,7 +2635,7 @@
         <v>8</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0112_-1_B.03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2696,7 +2696,7 @@
         <v>20</v>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0228_-1_LG.08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2757,7 +2757,7 @@
         <v>30</v>
       </c>
       <c r="F39" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0005_-1_B.01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2818,7 +2818,7 @@
         <v>120</v>
       </c>
       <c r="F40" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0113_02_2.36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2879,7 +2879,7 @@
         <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2940,7 +2940,7 @@
         <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3001,7 +3001,7 @@
         <v>216</v>
       </c>
       <c r="F43" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0001_01_1.264</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3062,7 +3062,7 @@
         <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3106,12 +3106,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0227_03_3.39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3184,7 +3184,7 @@
         <v>10</v>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0005_00_G.01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3245,7 +3245,7 @@
         <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3306,7 +3306,7 @@
         <v>12</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0228_11_11.06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3428,7 +3428,7 @@
         <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3472,12 +3472,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0008_-1_B.152</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0228_11_11.06</t>
+          <t>0227_02_2.54</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0228_07_7.01</t>
+          <t>0201_02_2.06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3672,7 +3672,7 @@
         <v>12</v>
       </c>
       <c r="F54" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0113_01M_01M.19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3733,7 +3733,7 @@
         <v>13</v>
       </c>
       <c r="F55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3777,12 +3777,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0113_01M_01M.19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3794,7 +3794,7 @@
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3916,7 +3916,7 @@
         <v>6</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0450_03_3.43</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3977,7 +3977,7 @@
         <v>12</v>
       </c>
       <c r="F59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0113_01M_01M.19</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4082,12 +4082,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4099,7 +4099,7 @@
         <v>12</v>
       </c>
       <c r="F61" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0335_00_G.17</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4343,7 +4343,7 @@
         <v>12</v>
       </c>
       <c r="F65" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4387,12 +4387,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0335_00_G.17</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0214_00_G.22</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4465,7 +4465,7 @@
         <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0001_01_1.264</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4526,7 +4526,7 @@
         <v>120</v>
       </c>
       <c r="F68" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4570,12 +4570,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0201_02_2.06</t>
+          <t>0201_07_7.14</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0113_00_G.205</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0005_-1_B.01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4831,7 +4831,7 @@
         <v>120</v>
       </c>
       <c r="F73" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5014,7 +5014,7 @@
         <v>10</v>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5058,12 +5058,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0113_01M_01M.19</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5136,7 +5136,7 @@
         <v>12</v>
       </c>
       <c r="F78" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0251_01_1.01</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0228_07_7.01</t>
+          <t>0214_01_1.10</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5380,7 +5380,7 @@
         <v>12</v>
       </c>
       <c r="F82" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0113_01M_01M.19</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0228_07_7.18</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5502,7 +5502,7 @@
         <v>20</v>
       </c>
       <c r="F84" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0227_03_3.54</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5624,7 +5624,7 @@
         <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0001_01_1.264</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5685,7 +5685,7 @@
         <v>90</v>
       </c>
       <c r="F87" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5746,7 +5746,7 @@
         <v>12</v>
       </c>
       <c r="F88" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5790,12 +5790,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5807,7 +5807,7 @@
         <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_02_2.03</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5868,7 +5868,7 @@
         <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5912,12 +5912,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5990,7 +5990,7 @@
         <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -6034,12 +6034,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6051,7 +6051,7 @@
         <v>15</v>
       </c>
       <c r="F93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6173,7 +6173,7 @@
         <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -6217,12 +6217,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6234,7 +6234,7 @@
         <v>12</v>
       </c>
       <c r="F96" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6278,12 +6278,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6295,7 +6295,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6339,12 +6339,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6356,7 +6356,7 @@
         <v>15</v>
       </c>
       <c r="F98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -6400,12 +6400,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0227_02_2.39</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6417,7 +6417,7 @@
         <v>12</v>
       </c>
       <c r="F99" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0228_09_9.01</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6478,7 +6478,7 @@
         <v>15</v>
       </c>
       <c r="F100" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6522,12 +6522,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6539,7 +6539,7 @@
         <v>10</v>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6600,7 +6600,7 @@
         <v>12</v>
       </c>
       <c r="F102" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0008_-1_B.152</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6661,7 +6661,7 @@
         <v>12</v>
       </c>
       <c r="F103" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0008_-1_B.152</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0008_-1_B.152</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6905,7 +6905,7 @@
         <v>12</v>
       </c>
       <c r="F107" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7027,7 +7027,7 @@
         <v>30</v>
       </c>
       <c r="F109" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -7071,12 +7071,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7088,7 +7088,7 @@
         <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -7132,12 +7132,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7149,7 +7149,7 @@
         <v>8</v>
       </c>
       <c r="F111" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -7193,12 +7193,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0227_03_3.39</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>5</v>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -7315,12 +7315,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7332,7 +7332,7 @@
         <v>5</v>
       </c>
       <c r="F114" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0227_02_2.54</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7393,7 +7393,7 @@
         <v>12</v>
       </c>
       <c r="F115" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0228_07_7.01</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7454,7 +7454,7 @@
         <v>10</v>
       </c>
       <c r="F116" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -7498,12 +7498,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0008_02_2.418</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7515,7 +7515,7 @@
         <v>10</v>
       </c>
       <c r="F117" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
